--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -19741,12 +19741,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -19771,12 +19771,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -19785,6 +19785,9 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -19795,17 +19798,17 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
@@ -19815,12 +19818,12 @@
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -19828,47 +19831,47 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19900,12 +19903,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19930,12 +19933,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N106" t="n">
@@ -19944,24 +19947,27 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>Australian bat lyssavirus infection</t>
+          <t>Lyssavirus infection (excluding rabies)</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -19976,7 +19982,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
@@ -19986,7 +19992,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
@@ -19996,12 +20002,12 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG106" t="inlineStr">
@@ -20021,12 +20027,12 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Australia NINDSS human Australian bat lyssavirus infection; explicitly distinct from rabies virus infection.</t>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
@@ -20039,7 +20045,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
@@ -20049,12 +20055,12 @@
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -20062,45 +20068,438 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
-      <c r="AV106" t="inlineStr">
+      <c r="AV107" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW106" t="inlineStr">
+      <c r="AW107" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
+      <c r="AX107" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY106" t="inlineStr">
+      <c r="AY107" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
+      <c r="AZ107" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA106" t="inlineStr">
+      <c r="BA107" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB106" t="inlineStr">
+      <c r="BB107" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC106" t="inlineStr">
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Australian bat lyssavirus infection</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>AU_NINDSS_current</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS human Australian bat lyssavirus infection; explicitly distinct from rabies virus infection.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN108" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -20222,7 +20621,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -20232,7 +20631,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -20252,7 +20651,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN108" t="b">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -20505,6 +20505,405 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20538,7 +20937,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -20621,7 +21020,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -20631,7 +21030,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -20651,7 +21050,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15705,7 +15705,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20899,6 +20899,405 @@
         </is>
       </c>
       <c r="BC110" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -20937,7 +21336,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21419,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -21030,7 +21429,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -21050,7 +21449,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -21303,6 +21303,405 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21336,7 +21735,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -21419,7 +21818,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -21429,7 +21828,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -21449,7 +21848,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -46989,6 +46989,405 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV238" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA238" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB238" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC238" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47022,7 +47421,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -47105,7 +47504,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -47115,7 +47514,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -47135,7 +47534,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
